--- a/TrackModel/Red Line.xlsx
+++ b/TrackModel/Red Line.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="846" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2EABCE2-FC0B-41EB-AC0C-A032B158767F}"/>
+  <xr:revisionPtr revIDLastSave="942" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80236F34-FE83-4932-97D8-CC984D4781B8}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -834,11 +834,9 @@
         <v>8.6</v>
       </c>
       <c r="R4" s="3">
-        <f>P4</f>
         <v>15.4</v>
       </c>
       <c r="S4" s="3">
-        <f>Q5</f>
         <v>8.1</v>
       </c>
     </row>
@@ -875,17 +873,15 @@
         <v>8.1</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" ref="R5:R68" si="0">P6</f>
         <v>17.399999999999999</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" ref="S5:S68" si="1">Q6</f>
         <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f t="shared" ref="A6:A69" si="2">A5</f>
+        <f t="shared" ref="A6:A69" si="0">A5</f>
         <v>Red</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -916,17 +912,15 @@
         <v>7.7</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="0"/>
         <v>18.100000000000001</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -957,17 +951,15 @@
         <v>7</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="0"/>
         <v>18.399999999999999</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" si="1"/>
         <v>6.1</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1003,17 +995,15 @@
         <v>6.1</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="0"/>
         <v>19.100000000000001</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.4000000000000004</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1049,20 +1039,18 @@
         <v>19.100000000000001</v>
       </c>
       <c r="Q9" s="3">
-        <v>4.4000000000000004</v>
+        <v>5.4</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="0"/>
         <v>20.2</v>
       </c>
       <c r="S9" s="3">
-        <f t="shared" si="1"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1096,17 +1084,15 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" si="0"/>
         <v>21.6</v>
       </c>
       <c r="S10" s="3">
-        <f t="shared" si="1"/>
         <v>5.3</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1137,17 +1123,15 @@
         <v>5.3</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="0"/>
         <v>22.7</v>
       </c>
       <c r="S11" s="3">
-        <f t="shared" si="1"/>
         <v>5.8</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1184,17 +1168,15 @@
         <v>5.8</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="0"/>
         <v>23.3</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1225,17 +1207,15 @@
         <v>7</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="0"/>
         <v>22.3</v>
       </c>
       <c r="S13" s="3">
-        <f t="shared" si="1"/>
         <v>8.1</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1269,17 +1249,15 @@
         <v>8.1</v>
       </c>
       <c r="R14" s="3">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="S14" s="3">
-        <f t="shared" si="1"/>
         <v>8.4</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1310,17 +1288,15 @@
         <v>8.4</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="0"/>
         <v>19.399999999999999</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1351,17 +1327,15 @@
         <v>8.6</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S16" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1392,17 +1366,15 @@
         <v>8.6</v>
       </c>
       <c r="R17" s="3">
-        <f t="shared" si="0"/>
         <v>16.7</v>
       </c>
       <c r="S17" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1436,17 +1408,15 @@
         <v>8.6</v>
       </c>
       <c r="R18" s="3">
-        <f t="shared" si="0"/>
         <v>15.4</v>
       </c>
       <c r="S18" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1489,17 +1459,15 @@
         <v>8.6</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="0"/>
         <v>15.2</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1533,17 +1501,15 @@
         <v>8.6</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" si="0"/>
         <v>14.9</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1575,17 +1541,15 @@
         <v>8.6</v>
       </c>
       <c r="R21" s="3">
-        <f t="shared" si="0"/>
         <v>14.2</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1616,17 +1580,15 @@
         <v>8.6</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1660,17 +1622,15 @@
         <v>8.6</v>
       </c>
       <c r="R23" s="3">
-        <f t="shared" si="0"/>
         <v>13.2</v>
       </c>
       <c r="S23" s="3">
-        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1707,17 +1667,15 @@
         <v>8.6</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="0"/>
         <v>12.1</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" si="1"/>
         <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1751,17 +1709,15 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" si="0"/>
         <v>11.4</v>
       </c>
       <c r="S25" s="3">
-        <f t="shared" si="1"/>
         <v>9.4</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1792,17 +1748,15 @@
         <v>9.4</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" si="1"/>
         <v>10.3</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1839,17 +1793,15 @@
         <v>10.3</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1882,18 +1834,22 @@
       <c r="N28" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="P28" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>10.8</v>
+      </c>
       <c r="R28" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S28" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1923,18 +1879,22 @@
       <c r="L29" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="P29" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>11.3</v>
+      </c>
       <c r="R29" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S29" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1967,18 +1927,22 @@
       <c r="K30" s="3">
         <v>76</v>
       </c>
+      <c r="P30" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>11.8</v>
+      </c>
       <c r="R30" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S30" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -2005,18 +1969,22 @@
       <c r="I31" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P31" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>12.3</v>
+      </c>
       <c r="R31" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S31" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2043,18 +2011,22 @@
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P32" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>12.8</v>
+      </c>
       <c r="R32" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S32" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -2081,18 +2053,22 @@
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P33" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>13.3</v>
+      </c>
       <c r="R33" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S33" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -2119,18 +2095,22 @@
       <c r="I34" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P34" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>13.8</v>
+      </c>
       <c r="R34" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S34" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -2157,18 +2137,22 @@
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P35" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>14.3</v>
+      </c>
       <c r="R35" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S35" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -2201,18 +2185,22 @@
       <c r="K36" s="3">
         <v>72</v>
       </c>
+      <c r="P36" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>14.8</v>
+      </c>
       <c r="R36" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S36" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -2242,18 +2230,22 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="P37" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>15.3</v>
+      </c>
       <c r="R37" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S37" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -2286,18 +2278,22 @@
       <c r="N38" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="P38" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>15.8</v>
+      </c>
       <c r="R38" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S38" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -2327,13 +2323,17 @@
       <c r="L39" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="P39" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>16.3</v>
+      </c>
       <c r="R39" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S39" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -2365,18 +2365,22 @@
       <c r="I40" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P40" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>16.8</v>
+      </c>
       <c r="R40" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S40" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -2409,18 +2413,22 @@
       <c r="K41" s="3">
         <v>71</v>
       </c>
+      <c r="P41" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>17.3</v>
+      </c>
       <c r="R41" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S41" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -2447,18 +2455,22 @@
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P42" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>17.8</v>
+      </c>
       <c r="R42" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S42" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -2485,18 +2497,22 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P43" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>18.3</v>
+      </c>
       <c r="R43" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S43" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -2523,18 +2539,22 @@
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P44" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>18.8</v>
+      </c>
       <c r="R44" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S44" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -2561,18 +2581,22 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P45" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>19.3</v>
+      </c>
       <c r="R45" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S45" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -2599,18 +2623,22 @@
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P46" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>19.8</v>
+      </c>
       <c r="R46" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S46" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -2646,18 +2674,22 @@
       <c r="L47" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="P47" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>20.3</v>
+      </c>
       <c r="R47" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S47" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2690,18 +2722,22 @@
       <c r="N48" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="P48" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>20.8</v>
+      </c>
       <c r="R48" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S48" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2731,18 +2767,22 @@
       <c r="L49" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="P49" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>21.3</v>
+      </c>
       <c r="R49" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="S49" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2772,18 +2812,22 @@
       <c r="O50" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P50" s="3">
+        <v>10.7</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>23</v>
+      </c>
       <c r="R50" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S50" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2813,18 +2857,22 @@
       <c r="N51" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="P51" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>24.1</v>
+      </c>
       <c r="R51" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S51" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2851,18 +2899,22 @@
       <c r="L52" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="P52" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R52" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="S52" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -2886,18 +2938,22 @@
       <c r="H53" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P53" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R53" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S53" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2921,18 +2977,22 @@
       <c r="H54" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P54" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R54" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="S54" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -2962,18 +3022,22 @@
       <c r="K55" s="3">
         <v>66</v>
       </c>
+      <c r="P55" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R55" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S55" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2997,18 +3061,22 @@
       <c r="H56" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P56" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R56" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S56" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -3032,18 +3100,22 @@
       <c r="H57" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P57" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R57" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S57" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -3067,18 +3139,22 @@
       <c r="H58" s="5">
         <v>-0.8660000000000001</v>
       </c>
+      <c r="P58" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>24.6</v>
+      </c>
       <c r="R58" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S58" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -3102,18 +3178,22 @@
       <c r="H59" s="5">
         <v>-0.4910000000000001</v>
       </c>
+      <c r="P59" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>23.8</v>
+      </c>
       <c r="R59" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -3137,18 +3217,22 @@
       <c r="H60" s="5">
         <v>-0.1160000000000001</v>
       </c>
+      <c r="P60" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>22.4</v>
+      </c>
       <c r="R60" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S60" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -3172,18 +3256,22 @@
       <c r="H61" s="5">
         <v>0.6339999999999999</v>
       </c>
+      <c r="P61" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>20.8</v>
+      </c>
       <c r="R61" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S61" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.600000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -3210,18 +3298,22 @@
       <c r="L62" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="P62" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>19.600000000000001</v>
+      </c>
       <c r="R62" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S62" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -3251,18 +3343,22 @@
       <c r="N63" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="P63" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>18.7</v>
+      </c>
       <c r="R63" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S63" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -3289,18 +3385,22 @@
       <c r="L64" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="P64" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>18.2</v>
+      </c>
       <c r="R64" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S64" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -3324,18 +3424,22 @@
       <c r="H65" s="5">
         <v>-0.1160000000000001</v>
       </c>
+      <c r="P65" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>19.7</v>
+      </c>
       <c r="R65" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S65" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -3359,18 +3463,22 @@
       <c r="H66" s="5">
         <v>-0.8660000000000001</v>
       </c>
+      <c r="P66" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>21.2</v>
+      </c>
       <c r="R66" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S66" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -3394,18 +3502,22 @@
       <c r="H67" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P67" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>23</v>
+      </c>
       <c r="R67" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S67" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -3429,18 +3541,22 @@
       <c r="H68" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P68" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>24</v>
+      </c>
       <c r="R68" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="S68" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>Red</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -3464,18 +3580,22 @@
       <c r="H69" s="5">
         <v>-1.2410000000000001</v>
       </c>
+      <c r="P69" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>24.3</v>
+      </c>
       <c r="R69" s="3">
-        <f t="shared" ref="R69:R79" si="3">P70</f>
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S69" s="3">
-        <f t="shared" ref="S69:S79" si="4">Q70</f>
-        <v>0</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
-        <f t="shared" ref="A70:A79" si="5">A69</f>
+        <f t="shared" ref="A70:A79" si="1">A69</f>
         <v>Red</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -3502,18 +3622,22 @@
       <c r="I70" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P70" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>20.6</v>
+      </c>
       <c r="R70" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S70" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -3540,18 +3664,22 @@
       <c r="I71" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P71" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>19.399999999999999</v>
+      </c>
       <c r="R71" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S71" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -3578,18 +3706,22 @@
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P72" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>18.7</v>
+      </c>
       <c r="R72" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S72" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -3616,18 +3748,22 @@
       <c r="I73" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P73" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>18</v>
+      </c>
       <c r="R73" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S73" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -3654,18 +3790,22 @@
       <c r="I74" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P74" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>18</v>
+      </c>
       <c r="R74" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S74" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -3692,18 +3832,22 @@
       <c r="I75" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P75" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>14.7</v>
+      </c>
       <c r="R75" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S75" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -3730,18 +3874,22 @@
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P76" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>13.5</v>
+      </c>
       <c r="R76" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S76" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -3768,18 +3916,22 @@
       <c r="I77" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P77" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>12.8</v>
+      </c>
       <c r="R77" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S77" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -3806,18 +3958,22 @@
       <c r="I78" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P78" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q78" s="3">
+        <v>12.1</v>
+      </c>
       <c r="R78" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>Red</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -3844,13 +4000,17 @@
       <c r="I79" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="P79" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Q79" s="3">
+        <v>12.1</v>
+      </c>
       <c r="R79" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">

--- a/TrackModel/Red Line.xlsx
+++ b/TrackModel/Red Line.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/dgs44_pitt_edu/Documents/Trains/TrackModel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="942" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80236F34-FE83-4932-97D8-CC984D4781B8}"/>
+  <xr:revisionPtr revIDLastSave="949" documentId="8_{D0660D75-C052-4898-8402-12AA78E71664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{785D1438-E6C9-4320-8B97-42EA503825CA}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
+    <workbookView xWindow="7875" yWindow="3660" windowWidth="21600" windowHeight="11295" xr2:uid="{C71A2FFE-490E-4D57-BAA4-DE7AC575C897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="61">
   <si>
     <t>A</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>18191A1B1C1D1E1F202122232425262728292A2B2C2D2E2F434445464748494A4B4C4D4E4F</t>
+  </si>
+  <si>
+    <t>Signal</t>
   </si>
 </sst>
 </file>
@@ -688,6 +691,9 @@
       <c r="S1" s="3">
         <v>18</v>
       </c>
+      <c r="T1" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -736,15 +742,18 @@
         <v>10</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -784,19 +793,18 @@
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>22</v>
       </c>
-      <c r="Q3" s="3">
-        <v>11</v>
-      </c>
       <c r="R3" s="3">
+        <v>11</v>
+      </c>
+      <c r="S3" s="3">
         <v>22</v>
       </c>
-      <c r="S3" s="3">
-        <v>11</v>
-      </c>
-      <c r="T3" s="3"/>
+      <c r="T3" s="3">
+        <v>11</v>
+      </c>
       <c r="U3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -827,16 +835,16 @@
       <c r="L4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>15.4</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="3">
         <v>8.6</v>
       </c>
-      <c r="R4" s="3">
-        <v>15.4</v>
-      </c>
       <c r="S4" s="3">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="T4" s="3">
         <v>8.1</v>
       </c>
     </row>
@@ -866,16 +874,16 @@
       <c r="H5" s="5">
         <v>0.75</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>16.399999999999999</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>8.1</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <v>17.399999999999999</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>7.7</v>
       </c>
     </row>
@@ -905,16 +913,16 @@
       <c r="H6" s="5">
         <v>1.5</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>17.399999999999999</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>7.7</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <v>18.100000000000001</v>
       </c>
-      <c r="S6" s="3">
+      <c r="T6" s="3">
         <v>7</v>
       </c>
     </row>
@@ -944,16 +952,16 @@
       <c r="H7" s="5">
         <v>2.5</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>18.100000000000001</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>7</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <v>18.399999999999999</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="3">
         <v>6.1</v>
       </c>
     </row>
@@ -988,16 +996,16 @@
       <c r="L8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18.399999999999999</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6.1</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19.100000000000001</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5.4</v>
       </c>
     </row>
@@ -1035,16 +1043,16 @@
       <c r="N9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19.100000000000001</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5.4</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20.2</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -1077,16 +1085,16 @@
       <c r="L10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20.2</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5.0999999999999996</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>21.6</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5.3</v>
       </c>
     </row>
@@ -1116,16 +1124,16 @@
       <c r="H11" s="5">
         <v>4.125</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>21.6</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>5.3</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <v>22.7</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <v>5.8</v>
       </c>
     </row>
@@ -1161,16 +1169,16 @@
       <c r="K12" s="3">
         <v>75</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22.7</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5.8</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23.3</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1200,16 +1208,16 @@
       <c r="H13" s="5">
         <v>4.125</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>23.3</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="3">
         <v>7</v>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <v>22.3</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <v>8.1</v>
       </c>
     </row>
@@ -1242,16 +1250,16 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>22.3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8.1</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>21</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8.4</v>
       </c>
     </row>
@@ -1281,16 +1289,16 @@
       <c r="H15" s="5">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8.4</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>19.399999999999999</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8.6</v>
       </c>
     </row>
@@ -1320,20 +1328,20 @@
       <c r="H16" s="5">
         <v>1.6</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>19.399999999999999</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <v>8.6</v>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <v>18</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1359,20 +1367,20 @@
       <c r="H17" s="5">
         <v>0.85000000000000009</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8.6</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16.7</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1401,20 +1409,20 @@
       <c r="L18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16.7</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8.6</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15.4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1452,20 +1460,20 @@
       <c r="N19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>15.4</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="R19" s="3">
         <v>8.6</v>
       </c>
-      <c r="R19" s="3">
+      <c r="S19" s="3">
         <v>15.2</v>
       </c>
-      <c r="S19" s="3">
+      <c r="T19" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1494,20 +1502,20 @@
       <c r="L20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15.2</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8.6</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14.9</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1534,20 +1542,20 @@
       <c r="H21" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14.9</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8.6</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14.2</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1573,20 +1581,20 @@
       <c r="H22" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14.2</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8.6</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13.5</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1615,20 +1623,20 @@
       <c r="L23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13.5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8.6</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13.2</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8.6</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1660,20 +1668,20 @@
       <c r="N24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13.2</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8.6</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12.1</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1702,20 +1710,20 @@
       <c r="L25" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q25" s="3">
         <v>12.1</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="R25" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R25" s="3">
+      <c r="S25" s="3">
         <v>11.4</v>
       </c>
-      <c r="S25" s="3">
+      <c r="T25" s="3">
         <v>9.4</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1741,20 +1749,20 @@
       <c r="H26" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11.4</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9.4</v>
       </c>
-      <c r="R26" s="3">
-        <v>11</v>
-      </c>
       <c r="S26" s="3">
+        <v>11</v>
+      </c>
+      <c r="T26" s="3">
         <v>10.3</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1786,20 +1794,20 @@
       <c r="L27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P27" s="3">
-        <v>11</v>
-      </c>
       <c r="Q27" s="3">
+        <v>11</v>
+      </c>
+      <c r="R27" s="3">
         <v>10.3</v>
       </c>
-      <c r="R27" s="3">
-        <v>11</v>
-      </c>
       <c r="S27" s="3">
+        <v>11</v>
+      </c>
+      <c r="T27" s="3">
         <v>10.8</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1834,20 +1842,20 @@
       <c r="N28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P28" s="3">
-        <v>11</v>
-      </c>
       <c r="Q28" s="3">
+        <v>11</v>
+      </c>
+      <c r="R28" s="3">
         <v>10.8</v>
       </c>
-      <c r="R28" s="3">
-        <v>11</v>
-      </c>
       <c r="S28" s="3">
+        <v>11</v>
+      </c>
+      <c r="T28" s="3">
         <v>11.3</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1879,20 +1887,20 @@
       <c r="L29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P29" s="3">
-        <v>11</v>
-      </c>
       <c r="Q29" s="3">
+        <v>11</v>
+      </c>
+      <c r="R29" s="3">
         <v>11.3</v>
       </c>
-      <c r="R29" s="3">
-        <v>11</v>
-      </c>
       <c r="S29" s="3">
+        <v>11</v>
+      </c>
+      <c r="T29" s="3">
         <v>11.8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1927,20 +1935,20 @@
       <c r="K30" s="3">
         <v>76</v>
       </c>
-      <c r="P30" s="3">
-        <v>11</v>
-      </c>
       <c r="Q30" s="3">
+        <v>11</v>
+      </c>
+      <c r="R30" s="3">
         <v>11.8</v>
       </c>
-      <c r="R30" s="3">
-        <v>11</v>
-      </c>
       <c r="S30" s="3">
+        <v>11</v>
+      </c>
+      <c r="T30" s="3">
         <v>12.3</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -1969,20 +1977,20 @@
       <c r="I31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P31" s="3">
-        <v>11</v>
-      </c>
       <c r="Q31" s="3">
+        <v>11</v>
+      </c>
+      <c r="R31" s="3">
         <v>12.3</v>
       </c>
-      <c r="R31" s="3">
-        <v>11</v>
-      </c>
       <c r="S31" s="3">
+        <v>11</v>
+      </c>
+      <c r="T31" s="3">
         <v>12.8</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2011,20 +2019,20 @@
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>11</v>
-      </c>
       <c r="Q32" s="3">
+        <v>11</v>
+      </c>
+      <c r="R32" s="3">
         <v>12.8</v>
       </c>
-      <c r="R32" s="3">
-        <v>11</v>
-      </c>
       <c r="S32" s="3">
+        <v>11</v>
+      </c>
+      <c r="T32" s="3">
         <v>13.3</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2053,20 +2061,20 @@
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3">
-        <v>11</v>
-      </c>
       <c r="Q33" s="3">
+        <v>11</v>
+      </c>
+      <c r="R33" s="3">
         <v>13.3</v>
       </c>
-      <c r="R33" s="3">
-        <v>11</v>
-      </c>
       <c r="S33" s="3">
+        <v>11</v>
+      </c>
+      <c r="T33" s="3">
         <v>13.8</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2095,20 +2103,20 @@
       <c r="I34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P34" s="3">
-        <v>11</v>
-      </c>
       <c r="Q34" s="3">
+        <v>11</v>
+      </c>
+      <c r="R34" s="3">
         <v>13.8</v>
       </c>
-      <c r="R34" s="3">
-        <v>11</v>
-      </c>
       <c r="S34" s="3">
+        <v>11</v>
+      </c>
+      <c r="T34" s="3">
         <v>14.3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2137,20 +2145,20 @@
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3">
-        <v>11</v>
-      </c>
       <c r="Q35" s="3">
+        <v>11</v>
+      </c>
+      <c r="R35" s="3">
         <v>14.3</v>
       </c>
-      <c r="R35" s="3">
-        <v>11</v>
-      </c>
       <c r="S35" s="3">
+        <v>11</v>
+      </c>
+      <c r="T35" s="3">
         <v>14.8</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2185,20 +2193,20 @@
       <c r="K36" s="3">
         <v>72</v>
       </c>
-      <c r="P36" s="3">
-        <v>11</v>
-      </c>
       <c r="Q36" s="3">
+        <v>11</v>
+      </c>
+      <c r="R36" s="3">
         <v>14.8</v>
       </c>
-      <c r="R36" s="3">
-        <v>11</v>
-      </c>
       <c r="S36" s="3">
+        <v>11</v>
+      </c>
+      <c r="T36" s="3">
         <v>15.3</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2230,20 +2238,20 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P37" s="3">
-        <v>11</v>
-      </c>
       <c r="Q37" s="3">
+        <v>11</v>
+      </c>
+      <c r="R37" s="3">
         <v>15.3</v>
       </c>
-      <c r="R37" s="3">
-        <v>11</v>
-      </c>
       <c r="S37" s="3">
+        <v>11</v>
+      </c>
+      <c r="T37" s="3">
         <v>15.8</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2278,20 +2286,20 @@
       <c r="N38" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P38" s="3">
-        <v>11</v>
-      </c>
       <c r="Q38" s="3">
+        <v>11</v>
+      </c>
+      <c r="R38" s="3">
         <v>15.8</v>
       </c>
-      <c r="R38" s="3">
-        <v>11</v>
-      </c>
       <c r="S38" s="3">
+        <v>11</v>
+      </c>
+      <c r="T38" s="3">
         <v>16.3</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2323,20 +2331,20 @@
       <c r="L39" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P39" s="3">
-        <v>11</v>
-      </c>
       <c r="Q39" s="3">
+        <v>11</v>
+      </c>
+      <c r="R39" s="3">
         <v>16.3</v>
       </c>
-      <c r="R39" s="3">
-        <v>11</v>
-      </c>
       <c r="S39" s="3">
+        <v>11</v>
+      </c>
+      <c r="T39" s="3">
         <v>16.8</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
         <f>A36</f>
         <v>Red</v>
@@ -2365,20 +2373,20 @@
       <c r="I40" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P40" s="3">
-        <v>11</v>
-      </c>
       <c r="Q40" s="3">
+        <v>11</v>
+      </c>
+      <c r="R40" s="3">
         <v>16.8</v>
       </c>
-      <c r="R40" s="3">
-        <v>11</v>
-      </c>
       <c r="S40" s="3">
+        <v>11</v>
+      </c>
+      <c r="T40" s="3">
         <v>17.3</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2413,20 +2421,20 @@
       <c r="K41" s="3">
         <v>71</v>
       </c>
-      <c r="P41" s="3">
-        <v>11</v>
-      </c>
       <c r="Q41" s="3">
+        <v>11</v>
+      </c>
+      <c r="R41" s="3">
         <v>17.3</v>
       </c>
-      <c r="R41" s="3">
-        <v>11</v>
-      </c>
       <c r="S41" s="3">
+        <v>11</v>
+      </c>
+      <c r="T41" s="3">
         <v>17.8</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2455,20 +2463,20 @@
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>11</v>
-      </c>
       <c r="Q42" s="3">
+        <v>11</v>
+      </c>
+      <c r="R42" s="3">
         <v>17.8</v>
       </c>
-      <c r="R42" s="3">
-        <v>11</v>
-      </c>
       <c r="S42" s="3">
+        <v>11</v>
+      </c>
+      <c r="T42" s="3">
         <v>18.3</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2497,20 +2505,20 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>11</v>
-      </c>
       <c r="Q43" s="3">
+        <v>11</v>
+      </c>
+      <c r="R43" s="3">
         <v>18.3</v>
       </c>
-      <c r="R43" s="3">
-        <v>11</v>
-      </c>
       <c r="S43" s="3">
+        <v>11</v>
+      </c>
+      <c r="T43" s="3">
         <v>18.8</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2539,20 +2547,20 @@
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>11</v>
-      </c>
       <c r="Q44" s="3">
+        <v>11</v>
+      </c>
+      <c r="R44" s="3">
         <v>18.8</v>
       </c>
-      <c r="R44" s="3">
-        <v>11</v>
-      </c>
       <c r="S44" s="3">
+        <v>11</v>
+      </c>
+      <c r="T44" s="3">
         <v>19.3</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2581,20 +2589,20 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
-        <v>11</v>
-      </c>
       <c r="Q45" s="3">
+        <v>11</v>
+      </c>
+      <c r="R45" s="3">
         <v>19.3</v>
       </c>
-      <c r="R45" s="3">
-        <v>11</v>
-      </c>
       <c r="S45" s="3">
+        <v>11</v>
+      </c>
+      <c r="T45" s="3">
         <v>19.8</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2623,20 +2631,20 @@
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
-        <v>11</v>
-      </c>
       <c r="Q46" s="3">
+        <v>11</v>
+      </c>
+      <c r="R46" s="3">
         <v>19.8</v>
       </c>
-      <c r="R46" s="3">
-        <v>11</v>
-      </c>
       <c r="S46" s="3">
+        <v>11</v>
+      </c>
+      <c r="T46" s="3">
         <v>20.3</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2674,20 +2682,20 @@
       <c r="L47" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="P47" s="3">
-        <v>11</v>
-      </c>
       <c r="Q47" s="3">
+        <v>11</v>
+      </c>
+      <c r="R47" s="3">
         <v>20.3</v>
       </c>
-      <c r="R47" s="3">
-        <v>11</v>
-      </c>
       <c r="S47" s="3">
+        <v>11</v>
+      </c>
+      <c r="T47" s="3">
         <v>20.8</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2722,20 +2730,20 @@
       <c r="N48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P48" s="3">
-        <v>11</v>
-      </c>
       <c r="Q48" s="3">
+        <v>11</v>
+      </c>
+      <c r="R48" s="3">
         <v>20.8</v>
       </c>
-      <c r="R48" s="3">
-        <v>11</v>
-      </c>
       <c r="S48" s="3">
+        <v>11</v>
+      </c>
+      <c r="T48" s="3">
         <v>21.3</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2767,20 +2775,20 @@
       <c r="L49" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="P49" s="3">
-        <v>11</v>
-      </c>
       <c r="Q49" s="3">
+        <v>11</v>
+      </c>
+      <c r="R49" s="3">
         <v>21.3</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10.7</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2812,20 +2820,20 @@
       <c r="O50" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P50" s="3">
+      <c r="Q50" s="3">
         <v>10.7</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="R50" s="3">
         <v>23</v>
       </c>
-      <c r="R50" s="3">
+      <c r="S50" s="3">
         <v>9.5</v>
       </c>
-      <c r="S50" s="3">
+      <c r="T50" s="3">
         <v>24.1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2857,20 +2865,20 @@
       <c r="N51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P51" s="3">
+      <c r="Q51" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="R51" s="3">
         <v>24.1</v>
       </c>
-      <c r="R51" s="3">
+      <c r="S51" s="3">
         <v>8</v>
       </c>
-      <c r="S51" s="3">
+      <c r="T51" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2899,20 +2907,20 @@
       <c r="L52" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24.6</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7.2</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2938,20 +2946,20 @@
       <c r="H53" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P53" s="3">
+      <c r="Q53" s="3">
         <v>7.2</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="R53" s="3">
         <v>24.6</v>
       </c>
-      <c r="R53" s="3">
+      <c r="S53" s="3">
         <v>6.4</v>
       </c>
-      <c r="S53" s="3">
+      <c r="T53" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -2977,20 +2985,20 @@
       <c r="H54" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6.4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24.6</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5.6</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3022,20 +3030,20 @@
       <c r="K55" s="3">
         <v>66</v>
       </c>
-      <c r="P55" s="3">
+      <c r="Q55" s="3">
         <v>5.6</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="R55" s="3">
         <v>24.6</v>
       </c>
-      <c r="R55" s="3">
+      <c r="S55" s="3">
         <v>5</v>
       </c>
-      <c r="S55" s="3">
+      <c r="T55" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3061,20 +3069,20 @@
       <c r="H56" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P56" s="3">
+      <c r="Q56" s="3">
         <v>5</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="R56" s="3">
         <v>24.6</v>
       </c>
-      <c r="R56" s="3">
+      <c r="S56" s="3">
         <v>4.2</v>
       </c>
-      <c r="S56" s="3">
+      <c r="T56" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3100,20 +3108,20 @@
       <c r="H57" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4.2</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24.6</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3.4</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24.6</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3139,20 +3147,20 @@
       <c r="H58" s="5">
         <v>-0.8660000000000001</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3.4</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24.6</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1.8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23.8</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3178,20 +3186,20 @@
       <c r="H59" s="5">
         <v>-0.4910000000000001</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1.8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23.8</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22.4</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3217,20 +3225,20 @@
       <c r="H60" s="5">
         <v>-0.1160000000000001</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22.4</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>0.8</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20.8</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3256,20 +3264,20 @@
       <c r="H61" s="5">
         <v>0.6339999999999999</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>0.8</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20.8</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3298,20 +3306,20 @@
       <c r="L62" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19.600000000000001</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1.6</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18.7</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3343,20 +3351,20 @@
       <c r="N63" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P63" s="3">
+      <c r="Q63" s="3">
         <v>1.6</v>
       </c>
-      <c r="Q63" s="3">
+      <c r="R63" s="3">
         <v>18.7</v>
       </c>
-      <c r="R63" s="3">
+      <c r="S63" s="3">
         <v>2.7</v>
       </c>
-      <c r="S63" s="3">
+      <c r="T63" s="3">
         <v>18.2</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3385,20 +3393,20 @@
       <c r="L64" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P64" s="3">
+      <c r="Q64" s="3">
         <v>2.7</v>
       </c>
-      <c r="Q64" s="3">
+      <c r="R64" s="3">
         <v>18.2</v>
       </c>
-      <c r="R64" s="3">
+      <c r="S64" s="3">
         <v>3.7</v>
       </c>
-      <c r="S64" s="3">
+      <c r="T64" s="3">
         <v>19.7</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3424,20 +3432,20 @@
       <c r="H65" s="5">
         <v>-0.1160000000000001</v>
       </c>
-      <c r="P65" s="3">
+      <c r="Q65" s="3">
         <v>3.7</v>
       </c>
-      <c r="Q65" s="3">
+      <c r="R65" s="3">
         <v>19.7</v>
       </c>
-      <c r="R65" s="3">
+      <c r="S65" s="3">
         <v>4</v>
       </c>
-      <c r="S65" s="3">
+      <c r="T65" s="3">
         <v>21.2</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3463,20 +3471,20 @@
       <c r="H66" s="5">
         <v>-0.8660000000000001</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21.2</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4.0999999999999996</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3502,20 +3510,20 @@
       <c r="H67" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P67" s="3">
+      <c r="Q67" s="3">
         <v>4.0999999999999996</v>
       </c>
-      <c r="Q67" s="3">
+      <c r="R67" s="3">
         <v>23</v>
       </c>
-      <c r="R67" s="3">
+      <c r="S67" s="3">
         <v>4.5</v>
       </c>
-      <c r="S67" s="3">
+      <c r="T67" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3541,20 +3549,20 @@
       <c r="H68" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P68" s="3">
+      <c r="Q68" s="3">
         <v>4.5</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="R68" s="3">
         <v>24</v>
       </c>
-      <c r="R68" s="3">
+      <c r="S68" s="3">
         <v>5.2</v>
       </c>
-      <c r="S68" s="3">
+      <c r="T68" s="3">
         <v>24.3</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Red</v>
@@ -3580,20 +3588,20 @@
       <c r="H69" s="5">
         <v>-1.2410000000000001</v>
       </c>
-      <c r="P69" s="3">
+      <c r="Q69" s="3">
         <v>5.2</v>
       </c>
-      <c r="Q69" s="3">
+      <c r="R69" s="3">
         <v>24.3</v>
       </c>
-      <c r="R69" s="3">
+      <c r="S69" s="3">
         <v>6.4</v>
       </c>
-      <c r="S69" s="3">
+      <c r="T69" s="3">
         <v>24.5</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
         <f t="shared" ref="A70:A79" si="1">A69</f>
         <v>Red</v>
@@ -3622,20 +3630,20 @@
       <c r="I70" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P70" s="3">
-        <v>11</v>
-      </c>
       <c r="Q70" s="3">
+        <v>11</v>
+      </c>
+      <c r="R70" s="3">
         <v>20.6</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>9.5</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3664,20 +3672,20 @@
       <c r="I71" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P71" s="3">
+      <c r="Q71" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="R71" s="3">
         <v>19.399999999999999</v>
       </c>
-      <c r="R71" s="3">
+      <c r="S71" s="3">
         <v>9.5</v>
       </c>
-      <c r="S71" s="3">
+      <c r="T71" s="3">
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3706,20 +3714,20 @@
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18.7</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9.5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3748,20 +3756,20 @@
       <c r="I73" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P73" s="3">
+      <c r="Q73" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q73" s="3">
+      <c r="R73" s="3">
         <v>18</v>
       </c>
-      <c r="R73" s="3">
+      <c r="S73" s="3">
         <v>9.5</v>
       </c>
-      <c r="S73" s="3">
+      <c r="T73" s="3">
         <v>18.7</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3790,20 +3798,20 @@
       <c r="I74" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P74" s="3">
+      <c r="Q74" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q74" s="3">
+      <c r="R74" s="3">
         <v>18</v>
       </c>
-      <c r="R74" s="3">
-        <v>11</v>
-      </c>
       <c r="S74" s="3">
+        <v>11</v>
+      </c>
+      <c r="T74" s="3">
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3832,20 +3840,20 @@
       <c r="I75" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P75" s="3">
-        <v>11</v>
-      </c>
       <c r="Q75" s="3">
+        <v>11</v>
+      </c>
+      <c r="R75" s="3">
         <v>14.7</v>
       </c>
-      <c r="R75" s="3">
+      <c r="S75" s="3">
         <v>9.5</v>
       </c>
-      <c r="S75" s="3">
+      <c r="T75" s="3">
         <v>14.2</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3874,20 +3882,20 @@
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13.5</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9.5</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14.2</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3916,20 +3924,20 @@
       <c r="I77" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P77" s="3">
+      <c r="Q77" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q77" s="3">
+      <c r="R77" s="3">
         <v>12.8</v>
       </c>
-      <c r="R77" s="3">
+      <c r="S77" s="3">
         <v>9.5</v>
       </c>
-      <c r="S77" s="3">
+      <c r="T77" s="3">
         <v>13.5</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -3958,20 +3966,20 @@
       <c r="I78" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P78" s="3">
+      <c r="Q78" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q78" s="3">
+      <c r="R78" s="3">
         <v>12.1</v>
       </c>
-      <c r="R78" s="3">
+      <c r="S78" s="3">
         <v>9.5</v>
       </c>
-      <c r="S78" s="3">
+      <c r="T78" s="3">
         <v>12.8</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Red</v>
@@ -4000,20 +4008,20 @@
       <c r="I79" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P79" s="3">
+      <c r="Q79" s="3">
         <v>9.5</v>
       </c>
-      <c r="Q79" s="3">
+      <c r="R79" s="3">
         <v>12.1</v>
       </c>
-      <c r="R79" s="3">
-        <v>11</v>
-      </c>
       <c r="S79" s="3">
+        <v>11</v>
+      </c>
+      <c r="T79" s="3">
         <v>11.7</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
